--- a/DSA5.xlsx
+++ b/DSA5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maksa\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Desktop\Repository\DSA-5-zadanie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AF276C4-49DA-4039-9D99-8A7BB74D5A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E88154-39F8-422A-9680-79660B13A7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{8F9471F4-396A-42B3-AC8C-8274B5264AEF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{8F9471F4-396A-42B3-AC8C-8274B5264AEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -142,7 +142,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1665,7 +1665,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3182,7 +3182,7 @@
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4697,7 +4697,7 @@
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6227,7 +6227,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7742,7 +7742,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9257,7 +9257,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10772,7 +10772,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12287,7 +12287,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13816,7 +13816,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15331,7 +15331,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -16846,7 +16846,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -25483,9 +25483,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -25523,7 +25523,7 @@
         <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
@@ -25629,7 +25629,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -25800,9 +25800,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF3C1CA-A2BA-4371-AFB2-F0F788A4E1D3}">
   <dimension ref="B1:I202"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>2</v>
       </c>
@@ -25813,7 +25813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -25833,7 +25833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>10</v>
       </c>
@@ -25853,7 +25853,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>500</v>
       </c>
@@ -25873,7 +25873,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -25893,7 +25893,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1500</v>
       </c>
@@ -25913,7 +25913,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2000</v>
       </c>
@@ -25933,7 +25933,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2500</v>
       </c>
@@ -25953,7 +25953,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>3000</v>
       </c>
@@ -25973,7 +25973,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>3500</v>
       </c>
@@ -25993,7 +25993,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>4000</v>
       </c>
@@ -26013,7 +26013,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>4500</v>
       </c>
@@ -26033,7 +26033,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>5000</v>
       </c>
@@ -26053,7 +26053,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>5500</v>
       </c>
@@ -26073,7 +26073,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>6000</v>
       </c>
@@ -26093,7 +26093,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>6500</v>
       </c>
@@ -26113,7 +26113,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>7000</v>
       </c>
@@ -26133,7 +26133,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>7500</v>
       </c>
@@ -26153,7 +26153,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>8000</v>
       </c>
@@ -26173,7 +26173,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>8500</v>
       </c>
@@ -26193,7 +26193,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>9000</v>
       </c>
@@ -26213,7 +26213,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>9500</v>
       </c>
@@ -26233,7 +26233,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>10000</v>
       </c>
@@ -26253,7 +26253,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>10500</v>
       </c>
@@ -26273,7 +26273,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>11000</v>
       </c>
@@ -26293,7 +26293,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>11500</v>
       </c>
@@ -26313,7 +26313,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>12000</v>
       </c>
@@ -26333,7 +26333,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>12500</v>
       </c>
@@ -26353,7 +26353,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>13000</v>
       </c>
@@ -26373,7 +26373,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>13500</v>
       </c>
@@ -26393,7 +26393,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>14000</v>
       </c>
@@ -26413,7 +26413,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>14500</v>
       </c>
@@ -26433,7 +26433,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>15000</v>
       </c>
@@ -26453,7 +26453,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>15500</v>
       </c>
@@ -26473,7 +26473,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>16000</v>
       </c>
@@ -26493,7 +26493,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>16500</v>
       </c>
@@ -26513,7 +26513,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>17000</v>
       </c>
@@ -26533,7 +26533,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>17500</v>
       </c>
@@ -26553,7 +26553,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>18000</v>
       </c>
@@ -26573,7 +26573,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>18500</v>
       </c>
@@ -26593,7 +26593,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>19000</v>
       </c>
@@ -26613,7 +26613,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>19500</v>
       </c>
@@ -26633,7 +26633,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>20000</v>
       </c>
@@ -26653,7 +26653,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>20500</v>
       </c>
@@ -26673,7 +26673,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>21000</v>
       </c>
@@ -26693,7 +26693,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>21500</v>
       </c>
@@ -26713,7 +26713,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>22000</v>
       </c>
@@ -26733,7 +26733,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>22500</v>
       </c>
@@ -26753,7 +26753,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>23000</v>
       </c>
@@ -26773,7 +26773,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>23500</v>
       </c>
@@ -26793,7 +26793,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>24000</v>
       </c>
@@ -26813,7 +26813,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>24500</v>
       </c>
@@ -26833,7 +26833,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>25000</v>
       </c>
@@ -26853,7 +26853,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>25500</v>
       </c>
@@ -26873,7 +26873,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>26000</v>
       </c>
@@ -26893,7 +26893,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>26500</v>
       </c>
@@ -26913,7 +26913,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>27000</v>
       </c>
@@ -26933,7 +26933,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>27500</v>
       </c>
@@ -26953,7 +26953,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>28000</v>
       </c>
@@ -26973,7 +26973,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>28500</v>
       </c>
@@ -26993,7 +26993,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>29000</v>
       </c>
@@ -27013,7 +27013,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>29500</v>
       </c>
@@ -27033,7 +27033,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>30000</v>
       </c>
@@ -27053,7 +27053,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>30500</v>
       </c>
@@ -27073,7 +27073,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>31000</v>
       </c>
@@ -27093,7 +27093,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>31500</v>
       </c>
@@ -27113,7 +27113,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>32000</v>
       </c>
@@ -27133,7 +27133,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>32500</v>
       </c>
@@ -27153,7 +27153,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>33000</v>
       </c>
@@ -27173,7 +27173,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>33500</v>
       </c>
@@ -27193,7 +27193,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>34000</v>
       </c>
@@ -27213,7 +27213,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>34500</v>
       </c>
@@ -27233,7 +27233,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>35000</v>
       </c>
@@ -27253,7 +27253,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>35500</v>
       </c>
@@ -27273,7 +27273,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>36000</v>
       </c>
@@ -27293,7 +27293,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>36500</v>
       </c>
@@ -27313,7 +27313,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>37000</v>
       </c>
@@ -27333,7 +27333,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>37500</v>
       </c>
@@ -27353,7 +27353,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>38000</v>
       </c>
@@ -27373,7 +27373,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>38500</v>
       </c>
@@ -27393,7 +27393,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>39000</v>
       </c>
@@ -27413,7 +27413,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>39500</v>
       </c>
@@ -27433,7 +27433,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>40000</v>
       </c>
@@ -27453,7 +27453,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>40500</v>
       </c>
@@ -27473,7 +27473,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>41000</v>
       </c>
@@ -27493,7 +27493,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>41500</v>
       </c>
@@ -27513,7 +27513,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>42000</v>
       </c>
@@ -27533,7 +27533,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>42500</v>
       </c>
@@ -27553,7 +27553,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>43000</v>
       </c>
@@ -27573,7 +27573,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>43500</v>
       </c>
@@ -27593,7 +27593,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>44000</v>
       </c>
@@ -27613,7 +27613,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>44500</v>
       </c>
@@ -27633,7 +27633,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>45000</v>
       </c>
@@ -27653,7 +27653,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>45500</v>
       </c>
@@ -27673,7 +27673,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>46000</v>
       </c>
@@ -27693,7 +27693,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>46500</v>
       </c>
@@ -27713,7 +27713,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>47000</v>
       </c>
@@ -27733,7 +27733,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>47500</v>
       </c>
@@ -27753,7 +27753,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>48000</v>
       </c>
@@ -27773,7 +27773,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>48500</v>
       </c>
@@ -27793,7 +27793,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>49000</v>
       </c>
@@ -27813,7 +27813,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>49500</v>
       </c>
@@ -27833,7 +27833,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>50000</v>
       </c>
@@ -27853,7 +27853,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>50500</v>
       </c>
@@ -27873,7 +27873,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>51000</v>
       </c>
@@ -27893,7 +27893,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>51500</v>
       </c>
@@ -27913,7 +27913,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>52000</v>
       </c>
@@ -27933,7 +27933,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>52500</v>
       </c>
@@ -27953,7 +27953,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>53000</v>
       </c>
@@ -27973,7 +27973,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>53500</v>
       </c>
@@ -27993,7 +27993,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>54000</v>
       </c>
@@ -28013,7 +28013,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B112">
         <v>54500</v>
       </c>
@@ -28033,7 +28033,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B113">
         <v>55000</v>
       </c>
@@ -28053,7 +28053,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B114">
         <v>55500</v>
       </c>
@@ -28073,7 +28073,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B115">
         <v>56000</v>
       </c>
@@ -28093,7 +28093,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B116">
         <v>56500</v>
       </c>
@@ -28113,7 +28113,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B117">
         <v>57000</v>
       </c>
@@ -28133,7 +28133,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B118">
         <v>57500</v>
       </c>
@@ -28153,7 +28153,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B119">
         <v>58000</v>
       </c>
@@ -28173,7 +28173,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B120">
         <v>58500</v>
       </c>
@@ -28193,7 +28193,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B121">
         <v>59000</v>
       </c>
@@ -28213,7 +28213,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B122">
         <v>59500</v>
       </c>
@@ -28233,7 +28233,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B123">
         <v>60000</v>
       </c>
@@ -28253,7 +28253,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B124">
         <v>60500</v>
       </c>
@@ -28273,7 +28273,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B125">
         <v>61000</v>
       </c>
@@ -28293,7 +28293,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B126">
         <v>61500</v>
       </c>
@@ -28313,7 +28313,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B127">
         <v>62000</v>
       </c>
@@ -28333,7 +28333,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B128">
         <v>62500</v>
       </c>
@@ -28353,7 +28353,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B129">
         <v>63000</v>
       </c>
@@ -28373,7 +28373,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>63500</v>
       </c>
@@ -28393,7 +28393,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B131">
         <v>64000</v>
       </c>
@@ -28413,7 +28413,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B132">
         <v>64500</v>
       </c>
@@ -28433,7 +28433,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B133">
         <v>65000</v>
       </c>
@@ -28453,7 +28453,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B134">
         <v>65500</v>
       </c>
@@ -28473,7 +28473,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B135">
         <v>66000</v>
       </c>
@@ -28493,7 +28493,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B136">
         <v>66500</v>
       </c>
@@ -28513,7 +28513,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B137">
         <v>67000</v>
       </c>
@@ -28533,7 +28533,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B138">
         <v>67500</v>
       </c>
@@ -28553,7 +28553,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B139">
         <v>68000</v>
       </c>
@@ -28573,7 +28573,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B140">
         <v>68500</v>
       </c>
@@ -28593,7 +28593,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B141">
         <v>69000</v>
       </c>
@@ -28613,7 +28613,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B142">
         <v>69500</v>
       </c>
@@ -28633,7 +28633,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B143">
         <v>70000</v>
       </c>
@@ -28653,7 +28653,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B144">
         <v>70500</v>
       </c>
@@ -28673,7 +28673,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B145">
         <v>71000</v>
       </c>
@@ -28693,7 +28693,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B146">
         <v>71500</v>
       </c>
@@ -28713,7 +28713,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B147">
         <v>72000</v>
       </c>
@@ -28733,7 +28733,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B148">
         <v>72500</v>
       </c>
@@ -28753,7 +28753,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B149">
         <v>73000</v>
       </c>
@@ -28773,7 +28773,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B150">
         <v>73500</v>
       </c>
@@ -28793,7 +28793,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B151">
         <v>74000</v>
       </c>
@@ -28813,7 +28813,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B152">
         <v>74500</v>
       </c>
@@ -28833,7 +28833,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B153">
         <v>75000</v>
       </c>
@@ -28853,7 +28853,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B154">
         <v>75500</v>
       </c>
@@ -28873,7 +28873,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B155">
         <v>76000</v>
       </c>
@@ -28893,7 +28893,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B156">
         <v>76500</v>
       </c>
@@ -28913,7 +28913,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B157">
         <v>77000</v>
       </c>
@@ -28933,7 +28933,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B158">
         <v>77500</v>
       </c>
@@ -28953,7 +28953,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B159">
         <v>78000</v>
       </c>
@@ -28973,7 +28973,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B160">
         <v>78500</v>
       </c>
@@ -28993,7 +28993,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B161">
         <v>79000</v>
       </c>
@@ -29013,7 +29013,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B162">
         <v>79500</v>
       </c>
@@ -29033,7 +29033,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B163">
         <v>80000</v>
       </c>
@@ -29053,7 +29053,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B164">
         <v>80500</v>
       </c>
@@ -29073,7 +29073,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B165">
         <v>81000</v>
       </c>
@@ -29093,7 +29093,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B166">
         <v>81500</v>
       </c>
@@ -29113,7 +29113,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B167">
         <v>82000</v>
       </c>
@@ -29133,7 +29133,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B168">
         <v>82500</v>
       </c>
@@ -29153,7 +29153,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B169">
         <v>83000</v>
       </c>
@@ -29173,7 +29173,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B170">
         <v>83500</v>
       </c>
@@ -29193,7 +29193,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B171">
         <v>84000</v>
       </c>
@@ -29213,7 +29213,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B172">
         <v>84500</v>
       </c>
@@ -29233,7 +29233,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B173">
         <v>85000</v>
       </c>
@@ -29253,7 +29253,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B174">
         <v>85500</v>
       </c>
@@ -29273,7 +29273,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B175">
         <v>86000</v>
       </c>
@@ -29293,7 +29293,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B176">
         <v>86500</v>
       </c>
@@ -29313,7 +29313,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B177">
         <v>87000</v>
       </c>
@@ -29333,7 +29333,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B178">
         <v>87500</v>
       </c>
@@ -29353,7 +29353,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B179">
         <v>88000</v>
       </c>
@@ -29373,7 +29373,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B180">
         <v>88500</v>
       </c>
@@ -29393,7 +29393,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B181">
         <v>89000</v>
       </c>
@@ -29413,7 +29413,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B182">
         <v>89500</v>
       </c>
@@ -29433,7 +29433,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B183">
         <v>90000</v>
       </c>
@@ -29453,7 +29453,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B184">
         <v>90500</v>
       </c>
@@ -29473,7 +29473,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B185">
         <v>91000</v>
       </c>
@@ -29493,7 +29493,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B186">
         <v>91500</v>
       </c>
@@ -29513,7 +29513,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B187">
         <v>92000</v>
       </c>
@@ -29533,7 +29533,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B188">
         <v>92500</v>
       </c>
@@ -29553,7 +29553,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B189">
         <v>93000</v>
       </c>
@@ -29573,7 +29573,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B190">
         <v>93500</v>
       </c>
@@ -29593,7 +29593,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B191">
         <v>94000</v>
       </c>
@@ -29613,7 +29613,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B192">
         <v>94500</v>
       </c>
@@ -29633,7 +29633,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B193">
         <v>95000</v>
       </c>
@@ -29653,7 +29653,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B194">
         <v>95500</v>
       </c>
@@ -29673,7 +29673,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B195">
         <v>96000</v>
       </c>
@@ -29693,7 +29693,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B196">
         <v>96500</v>
       </c>
@@ -29713,7 +29713,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B197">
         <v>97000</v>
       </c>
@@ -29733,7 +29733,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B198">
         <v>97500</v>
       </c>
@@ -29753,7 +29753,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B199">
         <v>98000</v>
       </c>
@@ -29773,7 +29773,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B200">
         <v>98500</v>
       </c>
@@ -29793,7 +29793,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B201">
         <v>99000</v>
       </c>
@@ -29813,7 +29813,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B202">
         <v>99500</v>
       </c>
@@ -29843,9 +29843,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF3AF336-99F5-4A65-919F-8B128D858E2C}">
   <dimension ref="B1:I202"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>5</v>
       </c>
@@ -29856,7 +29856,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -29876,7 +29876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>10</v>
       </c>
@@ -29896,7 +29896,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>500</v>
       </c>
@@ -29916,7 +29916,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -29936,7 +29936,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1500</v>
       </c>
@@ -29956,7 +29956,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2000</v>
       </c>
@@ -29976,7 +29976,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2500</v>
       </c>
@@ -29996,7 +29996,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>3000</v>
       </c>
@@ -30016,7 +30016,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>3500</v>
       </c>
@@ -30036,7 +30036,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>4000</v>
       </c>
@@ -30056,7 +30056,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>4500</v>
       </c>
@@ -30076,7 +30076,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>5000</v>
       </c>
@@ -30096,7 +30096,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>5500</v>
       </c>
@@ -30116,7 +30116,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>6000</v>
       </c>
@@ -30136,7 +30136,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>6500</v>
       </c>
@@ -30156,7 +30156,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>7000</v>
       </c>
@@ -30176,7 +30176,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>7500</v>
       </c>
@@ -30196,7 +30196,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>8000</v>
       </c>
@@ -30216,7 +30216,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>8500</v>
       </c>
@@ -30236,7 +30236,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>9000</v>
       </c>
@@ -30256,7 +30256,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>9500</v>
       </c>
@@ -30276,7 +30276,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>10000</v>
       </c>
@@ -30296,7 +30296,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>10500</v>
       </c>
@@ -30316,7 +30316,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>11000</v>
       </c>
@@ -30336,7 +30336,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>11500</v>
       </c>
@@ -30356,7 +30356,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>12000</v>
       </c>
@@ -30376,7 +30376,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>12500</v>
       </c>
@@ -30396,7 +30396,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>13000</v>
       </c>
@@ -30416,7 +30416,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>13500</v>
       </c>
@@ -30436,7 +30436,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>14000</v>
       </c>
@@ -30456,7 +30456,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>14500</v>
       </c>
@@ -30476,7 +30476,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>15000</v>
       </c>
@@ -30496,7 +30496,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>15500</v>
       </c>
@@ -30516,7 +30516,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>16000</v>
       </c>
@@ -30536,7 +30536,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>16500</v>
       </c>
@@ -30556,7 +30556,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>17000</v>
       </c>
@@ -30576,7 +30576,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>17500</v>
       </c>
@@ -30596,7 +30596,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>18000</v>
       </c>
@@ -30616,7 +30616,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>18500</v>
       </c>
@@ -30636,7 +30636,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>19000</v>
       </c>
@@ -30656,7 +30656,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>19500</v>
       </c>
@@ -30676,7 +30676,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>20000</v>
       </c>
@@ -30696,7 +30696,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>20500</v>
       </c>
@@ -30716,7 +30716,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>21000</v>
       </c>
@@ -30736,7 +30736,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>21500</v>
       </c>
@@ -30756,7 +30756,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>22000</v>
       </c>
@@ -30776,7 +30776,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>22500</v>
       </c>
@@ -30796,7 +30796,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>23000</v>
       </c>
@@ -30816,7 +30816,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>23500</v>
       </c>
@@ -30836,7 +30836,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>24000</v>
       </c>
@@ -30856,7 +30856,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>24500</v>
       </c>
@@ -30876,7 +30876,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>25000</v>
       </c>
@@ -30896,7 +30896,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>25500</v>
       </c>
@@ -30916,7 +30916,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>26000</v>
       </c>
@@ -30936,7 +30936,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>26500</v>
       </c>
@@ -30956,7 +30956,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>27000</v>
       </c>
@@ -30976,7 +30976,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>27500</v>
       </c>
@@ -30996,7 +30996,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>28000</v>
       </c>
@@ -31016,7 +31016,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>28500</v>
       </c>
@@ -31036,7 +31036,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>29000</v>
       </c>
@@ -31056,7 +31056,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>29500</v>
       </c>
@@ -31076,7 +31076,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>30000</v>
       </c>
@@ -31096,7 +31096,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>30500</v>
       </c>
@@ -31116,7 +31116,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>31000</v>
       </c>
@@ -31136,7 +31136,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>31500</v>
       </c>
@@ -31156,7 +31156,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>32000</v>
       </c>
@@ -31176,7 +31176,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>32500</v>
       </c>
@@ -31196,7 +31196,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>33000</v>
       </c>
@@ -31216,7 +31216,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>33500</v>
       </c>
@@ -31236,7 +31236,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>34000</v>
       </c>
@@ -31256,7 +31256,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>34500</v>
       </c>
@@ -31276,7 +31276,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>35000</v>
       </c>
@@ -31296,7 +31296,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>35500</v>
       </c>
@@ -31316,7 +31316,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>36000</v>
       </c>
@@ -31336,7 +31336,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>36500</v>
       </c>
@@ -31356,7 +31356,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>37000</v>
       </c>
@@ -31376,7 +31376,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>37500</v>
       </c>
@@ -31396,7 +31396,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>38000</v>
       </c>
@@ -31416,7 +31416,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>38500</v>
       </c>
@@ -31436,7 +31436,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>39000</v>
       </c>
@@ -31456,7 +31456,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>39500</v>
       </c>
@@ -31476,7 +31476,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>40000</v>
       </c>
@@ -31496,7 +31496,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>40500</v>
       </c>
@@ -31516,7 +31516,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>41000</v>
       </c>
@@ -31536,7 +31536,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>41500</v>
       </c>
@@ -31556,7 +31556,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>42000</v>
       </c>
@@ -31576,7 +31576,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>42500</v>
       </c>
@@ -31596,7 +31596,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>43000</v>
       </c>
@@ -31616,7 +31616,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>43500</v>
       </c>
@@ -31636,7 +31636,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>44000</v>
       </c>
@@ -31656,7 +31656,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>44500</v>
       </c>
@@ -31676,7 +31676,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>45000</v>
       </c>
@@ -31696,7 +31696,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>45500</v>
       </c>
@@ -31716,7 +31716,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>46000</v>
       </c>
@@ -31736,7 +31736,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>46500</v>
       </c>
@@ -31756,7 +31756,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>47000</v>
       </c>
@@ -31776,7 +31776,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>47500</v>
       </c>
@@ -31796,7 +31796,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>48000</v>
       </c>
@@ -31816,7 +31816,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>48500</v>
       </c>
@@ -31836,7 +31836,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>49000</v>
       </c>
@@ -31856,7 +31856,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>49500</v>
       </c>
@@ -31876,7 +31876,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>50000</v>
       </c>
@@ -31896,7 +31896,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>50500</v>
       </c>
@@ -31916,7 +31916,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>51000</v>
       </c>
@@ -31936,7 +31936,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>51500</v>
       </c>
@@ -31956,7 +31956,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>52000</v>
       </c>
@@ -31976,7 +31976,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>52500</v>
       </c>
@@ -31996,7 +31996,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>53000</v>
       </c>
@@ -32016,7 +32016,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>53500</v>
       </c>
@@ -32036,7 +32036,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>54000</v>
       </c>
@@ -32056,7 +32056,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B112">
         <v>54500</v>
       </c>
@@ -32076,7 +32076,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B113">
         <v>55000</v>
       </c>
@@ -32096,7 +32096,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B114">
         <v>55500</v>
       </c>
@@ -32116,7 +32116,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B115">
         <v>56000</v>
       </c>
@@ -32136,7 +32136,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B116">
         <v>56500</v>
       </c>
@@ -32156,7 +32156,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B117">
         <v>57000</v>
       </c>
@@ -32176,7 +32176,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B118">
         <v>57500</v>
       </c>
@@ -32196,7 +32196,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B119">
         <v>58000</v>
       </c>
@@ -32216,7 +32216,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B120">
         <v>58500</v>
       </c>
@@ -32236,7 +32236,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B121">
         <v>59000</v>
       </c>
@@ -32256,7 +32256,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B122">
         <v>59500</v>
       </c>
@@ -32276,7 +32276,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B123">
         <v>60000</v>
       </c>
@@ -32296,7 +32296,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B124">
         <v>60500</v>
       </c>
@@ -32316,7 +32316,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B125">
         <v>61000</v>
       </c>
@@ -32336,7 +32336,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B126">
         <v>61500</v>
       </c>
@@ -32356,7 +32356,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B127">
         <v>62000</v>
       </c>
@@ -32376,7 +32376,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B128">
         <v>62500</v>
       </c>
@@ -32396,7 +32396,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B129">
         <v>63000</v>
       </c>
@@ -32416,7 +32416,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>63500</v>
       </c>
@@ -32436,7 +32436,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B131">
         <v>64000</v>
       </c>
@@ -32456,7 +32456,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B132">
         <v>64500</v>
       </c>
@@ -32476,7 +32476,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B133">
         <v>65000</v>
       </c>
@@ -32496,7 +32496,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B134">
         <v>65500</v>
       </c>
@@ -32516,7 +32516,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B135">
         <v>66000</v>
       </c>
@@ -32536,7 +32536,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B136">
         <v>66500</v>
       </c>
@@ -32556,7 +32556,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B137">
         <v>67000</v>
       </c>
@@ -32576,7 +32576,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B138">
         <v>67500</v>
       </c>
@@ -32596,7 +32596,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B139">
         <v>68000</v>
       </c>
@@ -32616,7 +32616,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B140">
         <v>68500</v>
       </c>
@@ -32636,7 +32636,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B141">
         <v>69000</v>
       </c>
@@ -32656,7 +32656,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B142">
         <v>69500</v>
       </c>
@@ -32676,7 +32676,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B143">
         <v>70000</v>
       </c>
@@ -32696,7 +32696,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B144">
         <v>70500</v>
       </c>
@@ -32716,7 +32716,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B145">
         <v>71000</v>
       </c>
@@ -32736,7 +32736,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B146">
         <v>71500</v>
       </c>
@@ -32756,7 +32756,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B147">
         <v>72000</v>
       </c>
@@ -32776,7 +32776,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B148">
         <v>72500</v>
       </c>
@@ -32796,7 +32796,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B149">
         <v>73000</v>
       </c>
@@ -32816,7 +32816,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B150">
         <v>73500</v>
       </c>
@@ -32836,7 +32836,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B151">
         <v>74000</v>
       </c>
@@ -32856,7 +32856,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B152">
         <v>74500</v>
       </c>
@@ -32876,7 +32876,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B153">
         <v>75000</v>
       </c>
@@ -32896,7 +32896,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B154">
         <v>75500</v>
       </c>
@@ -32916,7 +32916,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B155">
         <v>76000</v>
       </c>
@@ -32936,7 +32936,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B156">
         <v>76500</v>
       </c>
@@ -32956,7 +32956,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B157">
         <v>77000</v>
       </c>
@@ -32976,7 +32976,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B158">
         <v>77500</v>
       </c>
@@ -32996,7 +32996,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B159">
         <v>78000</v>
       </c>
@@ -33016,7 +33016,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B160">
         <v>78500</v>
       </c>
@@ -33036,7 +33036,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B161">
         <v>79000</v>
       </c>
@@ -33056,7 +33056,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B162">
         <v>79500</v>
       </c>
@@ -33076,7 +33076,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B163">
         <v>80000</v>
       </c>
@@ -33096,7 +33096,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B164">
         <v>80500</v>
       </c>
@@ -33116,7 +33116,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B165">
         <v>81000</v>
       </c>
@@ -33136,7 +33136,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B166">
         <v>81500</v>
       </c>
@@ -33156,7 +33156,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B167">
         <v>82000</v>
       </c>
@@ -33176,7 +33176,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B168">
         <v>82500</v>
       </c>
@@ -33196,7 +33196,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B169">
         <v>83000</v>
       </c>
@@ -33216,7 +33216,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B170">
         <v>83500</v>
       </c>
@@ -33236,7 +33236,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B171">
         <v>84000</v>
       </c>
@@ -33256,7 +33256,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B172">
         <v>84500</v>
       </c>
@@ -33276,7 +33276,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B173">
         <v>85000</v>
       </c>
@@ -33296,7 +33296,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B174">
         <v>85500</v>
       </c>
@@ -33316,7 +33316,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B175">
         <v>86000</v>
       </c>
@@ -33336,7 +33336,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B176">
         <v>86500</v>
       </c>
@@ -33356,7 +33356,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B177">
         <v>87000</v>
       </c>
@@ -33376,7 +33376,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B178">
         <v>87500</v>
       </c>
@@ -33396,7 +33396,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B179">
         <v>88000</v>
       </c>
@@ -33416,7 +33416,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B180">
         <v>88500</v>
       </c>
@@ -33436,7 +33436,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B181">
         <v>89000</v>
       </c>
@@ -33456,7 +33456,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B182">
         <v>89500</v>
       </c>
@@ -33476,7 +33476,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B183">
         <v>90000</v>
       </c>
@@ -33496,7 +33496,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B184">
         <v>90500</v>
       </c>
@@ -33516,7 +33516,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B185">
         <v>91000</v>
       </c>
@@ -33536,7 +33536,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B186">
         <v>91500</v>
       </c>
@@ -33556,7 +33556,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B187">
         <v>92000</v>
       </c>
@@ -33576,7 +33576,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B188">
         <v>92500</v>
       </c>
@@ -33596,7 +33596,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B189">
         <v>93000</v>
       </c>
@@ -33616,7 +33616,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B190">
         <v>93500</v>
       </c>
@@ -33636,7 +33636,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B191">
         <v>94000</v>
       </c>
@@ -33656,7 +33656,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B192">
         <v>94500</v>
       </c>
@@ -33676,7 +33676,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B193">
         <v>95000</v>
       </c>
@@ -33696,7 +33696,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B194">
         <v>95500</v>
       </c>
@@ -33716,7 +33716,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B195">
         <v>96000</v>
       </c>
@@ -33736,7 +33736,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B196">
         <v>96500</v>
       </c>
@@ -33756,7 +33756,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B197">
         <v>97000</v>
       </c>
@@ -33776,7 +33776,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B198">
         <v>97500</v>
       </c>
@@ -33796,7 +33796,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B199">
         <v>98000</v>
       </c>
@@ -33816,7 +33816,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B200">
         <v>98500</v>
       </c>
@@ -33836,7 +33836,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B201">
         <v>99000</v>
       </c>
@@ -33856,7 +33856,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B202">
         <v>99500</v>
       </c>
@@ -33886,9 +33886,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{199D6A40-25B5-483D-A2C3-0481106B643F}">
   <dimension ref="B1:I202"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>8</v>
       </c>
@@ -33899,7 +33899,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -33919,7 +33919,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>10</v>
       </c>
@@ -33939,7 +33939,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>500</v>
       </c>
@@ -33959,7 +33959,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -33979,7 +33979,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1500</v>
       </c>
@@ -33999,7 +33999,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2000</v>
       </c>
@@ -34019,7 +34019,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2500</v>
       </c>
@@ -34039,7 +34039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>3000</v>
       </c>
@@ -34059,7 +34059,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>3500</v>
       </c>
@@ -34079,7 +34079,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>4000</v>
       </c>
@@ -34099,7 +34099,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>4500</v>
       </c>
@@ -34119,7 +34119,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>5000</v>
       </c>
@@ -34139,7 +34139,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>5500</v>
       </c>
@@ -34159,7 +34159,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>6000</v>
       </c>
@@ -34179,7 +34179,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>6500</v>
       </c>
@@ -34199,7 +34199,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>7000</v>
       </c>
@@ -34219,7 +34219,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>7500</v>
       </c>
@@ -34239,7 +34239,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>8000</v>
       </c>
@@ -34259,7 +34259,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>8500</v>
       </c>
@@ -34279,7 +34279,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>9000</v>
       </c>
@@ -34299,7 +34299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>9500</v>
       </c>
@@ -34319,7 +34319,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>10000</v>
       </c>
@@ -34339,7 +34339,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>10500</v>
       </c>
@@ -34359,7 +34359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>11000</v>
       </c>
@@ -34379,7 +34379,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>11500</v>
       </c>
@@ -34399,7 +34399,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>12000</v>
       </c>
@@ -34419,7 +34419,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>12500</v>
       </c>
@@ -34439,7 +34439,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>13000</v>
       </c>
@@ -34459,7 +34459,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>13500</v>
       </c>
@@ -34479,7 +34479,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>14000</v>
       </c>
@@ -34499,7 +34499,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>14500</v>
       </c>
@@ -34519,7 +34519,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>15000</v>
       </c>
@@ -34539,7 +34539,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>15500</v>
       </c>
@@ -34559,7 +34559,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>16000</v>
       </c>
@@ -34579,7 +34579,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>16500</v>
       </c>
@@ -34599,7 +34599,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>17000</v>
       </c>
@@ -34619,7 +34619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>17500</v>
       </c>
@@ -34639,7 +34639,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>18000</v>
       </c>
@@ -34659,7 +34659,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>18500</v>
       </c>
@@ -34679,7 +34679,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>19000</v>
       </c>
@@ -34699,7 +34699,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>19500</v>
       </c>
@@ -34719,7 +34719,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>20000</v>
       </c>
@@ -34739,7 +34739,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>20500</v>
       </c>
@@ -34759,7 +34759,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>21000</v>
       </c>
@@ -34779,7 +34779,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>21500</v>
       </c>
@@ -34799,7 +34799,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>22000</v>
       </c>
@@ -34819,7 +34819,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>22500</v>
       </c>
@@ -34839,7 +34839,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>23000</v>
       </c>
@@ -34859,7 +34859,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>23500</v>
       </c>
@@ -34879,7 +34879,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>24000</v>
       </c>
@@ -34899,7 +34899,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>24500</v>
       </c>
@@ -34919,7 +34919,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>25000</v>
       </c>
@@ -34939,7 +34939,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>25500</v>
       </c>
@@ -34959,7 +34959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>26000</v>
       </c>
@@ -34979,7 +34979,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>26500</v>
       </c>
@@ -34999,7 +34999,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>27000</v>
       </c>
@@ -35019,7 +35019,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>27500</v>
       </c>
@@ -35039,7 +35039,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>28000</v>
       </c>
@@ -35059,7 +35059,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>28500</v>
       </c>
@@ -35079,7 +35079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>29000</v>
       </c>
@@ -35099,7 +35099,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>29500</v>
       </c>
@@ -35119,7 +35119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>30000</v>
       </c>
@@ -35139,7 +35139,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>30500</v>
       </c>
@@ -35159,7 +35159,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>31000</v>
       </c>
@@ -35179,7 +35179,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>31500</v>
       </c>
@@ -35199,7 +35199,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>32000</v>
       </c>
@@ -35219,7 +35219,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>32500</v>
       </c>
@@ -35239,7 +35239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>33000</v>
       </c>
@@ -35259,7 +35259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>33500</v>
       </c>
@@ -35279,7 +35279,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>34000</v>
       </c>
@@ -35299,7 +35299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>34500</v>
       </c>
@@ -35319,7 +35319,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>35000</v>
       </c>
@@ -35339,7 +35339,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>35500</v>
       </c>
@@ -35359,7 +35359,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>36000</v>
       </c>
@@ -35379,7 +35379,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>36500</v>
       </c>
@@ -35399,7 +35399,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>37000</v>
       </c>
@@ -35419,7 +35419,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>37500</v>
       </c>
@@ -35439,7 +35439,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>38000</v>
       </c>
@@ -35459,7 +35459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>38500</v>
       </c>
@@ -35479,7 +35479,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>39000</v>
       </c>
@@ -35499,7 +35499,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>39500</v>
       </c>
@@ -35519,7 +35519,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>40000</v>
       </c>
@@ -35539,7 +35539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>40500</v>
       </c>
@@ -35559,7 +35559,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>41000</v>
       </c>
@@ -35579,7 +35579,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>41500</v>
       </c>
@@ -35599,7 +35599,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>42000</v>
       </c>
@@ -35619,7 +35619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>42500</v>
       </c>
@@ -35639,7 +35639,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>43000</v>
       </c>
@@ -35659,7 +35659,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>43500</v>
       </c>
@@ -35679,7 +35679,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>44000</v>
       </c>
@@ -35699,7 +35699,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>44500</v>
       </c>
@@ -35719,7 +35719,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>45000</v>
       </c>
@@ -35739,7 +35739,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>45500</v>
       </c>
@@ -35759,7 +35759,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>46000</v>
       </c>
@@ -35779,7 +35779,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>46500</v>
       </c>
@@ -35799,7 +35799,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>47000</v>
       </c>
@@ -35819,7 +35819,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>47500</v>
       </c>
@@ -35839,7 +35839,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>48000</v>
       </c>
@@ -35859,7 +35859,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>48500</v>
       </c>
@@ -35879,7 +35879,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>49000</v>
       </c>
@@ -35899,7 +35899,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>49500</v>
       </c>
@@ -35919,7 +35919,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>50000</v>
       </c>
@@ -35939,7 +35939,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>50500</v>
       </c>
@@ -35959,7 +35959,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>51000</v>
       </c>
@@ -35979,7 +35979,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>51500</v>
       </c>
@@ -35999,7 +35999,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>52000</v>
       </c>
@@ -36019,7 +36019,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>52500</v>
       </c>
@@ -36039,7 +36039,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>53000</v>
       </c>
@@ -36059,7 +36059,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>53500</v>
       </c>
@@ -36079,7 +36079,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>54000</v>
       </c>
@@ -36099,7 +36099,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B112">
         <v>54500</v>
       </c>
@@ -36119,7 +36119,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B113">
         <v>55000</v>
       </c>
@@ -36139,7 +36139,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B114">
         <v>55500</v>
       </c>
@@ -36159,7 +36159,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B115">
         <v>56000</v>
       </c>
@@ -36179,7 +36179,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B116">
         <v>56500</v>
       </c>
@@ -36199,7 +36199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B117">
         <v>57000</v>
       </c>
@@ -36219,7 +36219,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B118">
         <v>57500</v>
       </c>
@@ -36239,7 +36239,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B119">
         <v>58000</v>
       </c>
@@ -36259,7 +36259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B120">
         <v>58500</v>
       </c>
@@ -36279,7 +36279,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B121">
         <v>59000</v>
       </c>
@@ -36299,7 +36299,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B122">
         <v>59500</v>
       </c>
@@ -36319,7 +36319,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B123">
         <v>60000</v>
       </c>
@@ -36339,7 +36339,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B124">
         <v>60500</v>
       </c>
@@ -36359,7 +36359,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B125">
         <v>61000</v>
       </c>
@@ -36379,7 +36379,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B126">
         <v>61500</v>
       </c>
@@ -36399,7 +36399,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B127">
         <v>62000</v>
       </c>
@@ -36419,7 +36419,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B128">
         <v>62500</v>
       </c>
@@ -36439,7 +36439,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B129">
         <v>63000</v>
       </c>
@@ -36459,7 +36459,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>63500</v>
       </c>
@@ -36479,7 +36479,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B131">
         <v>64000</v>
       </c>
@@ -36499,7 +36499,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B132">
         <v>64500</v>
       </c>
@@ -36519,7 +36519,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B133">
         <v>65000</v>
       </c>
@@ -36539,7 +36539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B134">
         <v>65500</v>
       </c>
@@ -36559,7 +36559,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B135">
         <v>66000</v>
       </c>
@@ -36579,7 +36579,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B136">
         <v>66500</v>
       </c>
@@ -36599,7 +36599,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B137">
         <v>67000</v>
       </c>
@@ -36619,7 +36619,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B138">
         <v>67500</v>
       </c>
@@ -36639,7 +36639,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B139">
         <v>68000</v>
       </c>
@@ -36659,7 +36659,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B140">
         <v>68500</v>
       </c>
@@ -36679,7 +36679,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B141">
         <v>69000</v>
       </c>
@@ -36699,7 +36699,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B142">
         <v>69500</v>
       </c>
@@ -36719,7 +36719,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B143">
         <v>70000</v>
       </c>
@@ -36739,7 +36739,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B144">
         <v>70500</v>
       </c>
@@ -36759,7 +36759,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B145">
         <v>71000</v>
       </c>
@@ -36779,7 +36779,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B146">
         <v>71500</v>
       </c>
@@ -36799,7 +36799,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B147">
         <v>72000</v>
       </c>
@@ -36819,7 +36819,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B148">
         <v>72500</v>
       </c>
@@ -36839,7 +36839,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B149">
         <v>73000</v>
       </c>
@@ -36859,7 +36859,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B150">
         <v>73500</v>
       </c>
@@ -36879,7 +36879,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B151">
         <v>74000</v>
       </c>
@@ -36899,7 +36899,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B152">
         <v>74500</v>
       </c>
@@ -36919,7 +36919,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B153">
         <v>75000</v>
       </c>
@@ -36939,7 +36939,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B154">
         <v>75500</v>
       </c>
@@ -36959,7 +36959,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B155">
         <v>76000</v>
       </c>
@@ -36979,7 +36979,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B156">
         <v>76500</v>
       </c>
@@ -36999,7 +36999,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B157">
         <v>77000</v>
       </c>
@@ -37019,7 +37019,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B158">
         <v>77500</v>
       </c>
@@ -37039,7 +37039,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B159">
         <v>78000</v>
       </c>
@@ -37059,7 +37059,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B160">
         <v>78500</v>
       </c>
@@ -37079,7 +37079,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B161">
         <v>79000</v>
       </c>
@@ -37099,7 +37099,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B162">
         <v>79500</v>
       </c>
@@ -37119,7 +37119,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B163">
         <v>80000</v>
       </c>
@@ -37139,7 +37139,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B164">
         <v>80500</v>
       </c>
@@ -37159,7 +37159,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B165">
         <v>81000</v>
       </c>
@@ -37179,7 +37179,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B166">
         <v>81500</v>
       </c>
@@ -37199,7 +37199,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B167">
         <v>82000</v>
       </c>
@@ -37219,7 +37219,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B168">
         <v>82500</v>
       </c>
@@ -37239,7 +37239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B169">
         <v>83000</v>
       </c>
@@ -37259,7 +37259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B170">
         <v>83500</v>
       </c>
@@ -37279,7 +37279,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B171">
         <v>84000</v>
       </c>
@@ -37299,7 +37299,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B172">
         <v>84500</v>
       </c>
@@ -37319,7 +37319,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B173">
         <v>85000</v>
       </c>
@@ -37339,7 +37339,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B174">
         <v>85500</v>
       </c>
@@ -37359,7 +37359,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B175">
         <v>86000</v>
       </c>
@@ -37379,7 +37379,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B176">
         <v>86500</v>
       </c>
@@ -37399,7 +37399,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B177">
         <v>87000</v>
       </c>
@@ -37419,7 +37419,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B178">
         <v>87500</v>
       </c>
@@ -37439,7 +37439,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B179">
         <v>88000</v>
       </c>
@@ -37459,7 +37459,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B180">
         <v>88500</v>
       </c>
@@ -37479,7 +37479,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B181">
         <v>89000</v>
       </c>
@@ -37499,7 +37499,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B182">
         <v>89500</v>
       </c>
@@ -37519,7 +37519,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B183">
         <v>90000</v>
       </c>
@@ -37539,7 +37539,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B184">
         <v>90500</v>
       </c>
@@ -37559,7 +37559,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B185">
         <v>91000</v>
       </c>
@@ -37579,7 +37579,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B186">
         <v>91500</v>
       </c>
@@ -37599,7 +37599,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B187">
         <v>92000</v>
       </c>
@@ -37619,7 +37619,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B188">
         <v>92500</v>
       </c>
@@ -37639,7 +37639,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B189">
         <v>93000</v>
       </c>
@@ -37659,7 +37659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B190">
         <v>93500</v>
       </c>
@@ -37679,7 +37679,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B191">
         <v>94000</v>
       </c>
@@ -37699,7 +37699,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B192">
         <v>94500</v>
       </c>
@@ -37719,7 +37719,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B193">
         <v>95000</v>
       </c>
@@ -37739,7 +37739,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B194">
         <v>95500</v>
       </c>
@@ -37759,7 +37759,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B195">
         <v>96000</v>
       </c>
@@ -37779,7 +37779,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B196">
         <v>96500</v>
       </c>
@@ -37799,7 +37799,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B197">
         <v>97000</v>
       </c>
@@ -37819,7 +37819,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B198">
         <v>97500</v>
       </c>
@@ -37839,7 +37839,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B199">
         <v>98000</v>
       </c>
@@ -37859,7 +37859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B200">
         <v>98500</v>
       </c>
@@ -37879,7 +37879,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B201">
         <v>99000</v>
       </c>
@@ -37899,7 +37899,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B202">
         <v>99500</v>
       </c>
@@ -37929,9 +37929,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{837C9785-DB73-493E-8FD4-13BD37718F1A}">
   <dimension ref="B1:I202"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>11</v>
       </c>
@@ -37942,7 +37942,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -37962,7 +37962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>10</v>
       </c>
@@ -37982,7 +37982,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>500</v>
       </c>
@@ -38002,7 +38002,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -38022,7 +38022,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1500</v>
       </c>
@@ -38042,7 +38042,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2000</v>
       </c>
@@ -38062,7 +38062,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2500</v>
       </c>
@@ -38082,7 +38082,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>3000</v>
       </c>
@@ -38102,7 +38102,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>3500</v>
       </c>
@@ -38122,7 +38122,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>4000</v>
       </c>
@@ -38142,7 +38142,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>4500</v>
       </c>
@@ -38162,7 +38162,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>5000</v>
       </c>
@@ -38182,7 +38182,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>5500</v>
       </c>
@@ -38202,7 +38202,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>6000</v>
       </c>
@@ -38222,7 +38222,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>6500</v>
       </c>
@@ -38242,7 +38242,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>7000</v>
       </c>
@@ -38262,7 +38262,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>7500</v>
       </c>
@@ -38282,7 +38282,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>8000</v>
       </c>
@@ -38302,7 +38302,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>8500</v>
       </c>
@@ -38322,7 +38322,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>9000</v>
       </c>
@@ -38342,7 +38342,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>9500</v>
       </c>
@@ -38362,7 +38362,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>10000</v>
       </c>
@@ -38382,7 +38382,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>10500</v>
       </c>
@@ -38402,7 +38402,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>11000</v>
       </c>
@@ -38422,7 +38422,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>11500</v>
       </c>
@@ -38442,7 +38442,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>12000</v>
       </c>
@@ -38462,7 +38462,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>12500</v>
       </c>
@@ -38482,7 +38482,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>13000</v>
       </c>
@@ -38502,7 +38502,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>13500</v>
       </c>
@@ -38522,7 +38522,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>14000</v>
       </c>
@@ -38542,7 +38542,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>14500</v>
       </c>
@@ -38562,7 +38562,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>15000</v>
       </c>
@@ -38582,7 +38582,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>15500</v>
       </c>
@@ -38602,7 +38602,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>16000</v>
       </c>
@@ -38622,7 +38622,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>16500</v>
       </c>
@@ -38642,7 +38642,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>17000</v>
       </c>
@@ -38662,7 +38662,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>17500</v>
       </c>
@@ -38682,7 +38682,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>18000</v>
       </c>
@@ -38702,7 +38702,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>18500</v>
       </c>
@@ -38722,7 +38722,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>19000</v>
       </c>
@@ -38742,7 +38742,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>19500</v>
       </c>
@@ -38762,7 +38762,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>20000</v>
       </c>
@@ -38782,7 +38782,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>20500</v>
       </c>
@@ -38802,7 +38802,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>21000</v>
       </c>
@@ -38822,7 +38822,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>21500</v>
       </c>
@@ -38842,7 +38842,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>22000</v>
       </c>
@@ -38862,7 +38862,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>22500</v>
       </c>
@@ -38882,7 +38882,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>23000</v>
       </c>
@@ -38902,7 +38902,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>23500</v>
       </c>
@@ -38922,7 +38922,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>24000</v>
       </c>
@@ -38942,7 +38942,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>24500</v>
       </c>
@@ -38962,7 +38962,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>25000</v>
       </c>
@@ -38982,7 +38982,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>25500</v>
       </c>
@@ -39002,7 +39002,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>26000</v>
       </c>
@@ -39022,7 +39022,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>26500</v>
       </c>
@@ -39042,7 +39042,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>27000</v>
       </c>
@@ -39062,7 +39062,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>27500</v>
       </c>
@@ -39082,7 +39082,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>28000</v>
       </c>
@@ -39102,7 +39102,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>28500</v>
       </c>
@@ -39122,7 +39122,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>29000</v>
       </c>
@@ -39142,7 +39142,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>29500</v>
       </c>
@@ -39162,7 +39162,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>30000</v>
       </c>
@@ -39182,7 +39182,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>30500</v>
       </c>
@@ -39202,7 +39202,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>31000</v>
       </c>
@@ -39222,7 +39222,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>31500</v>
       </c>
@@ -39242,7 +39242,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>32000</v>
       </c>
@@ -39262,7 +39262,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>32500</v>
       </c>
@@ -39282,7 +39282,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>33000</v>
       </c>
@@ -39302,7 +39302,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>33500</v>
       </c>
@@ -39322,7 +39322,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>34000</v>
       </c>
@@ -39342,7 +39342,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>34500</v>
       </c>
@@ -39362,7 +39362,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>35000</v>
       </c>
@@ -39382,7 +39382,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>35500</v>
       </c>
@@ -39402,7 +39402,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>36000</v>
       </c>
@@ -39422,7 +39422,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>36500</v>
       </c>
@@ -39442,7 +39442,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>37000</v>
       </c>
@@ -39462,7 +39462,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>37500</v>
       </c>
@@ -39482,7 +39482,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>38000</v>
       </c>
@@ -39502,7 +39502,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>38500</v>
       </c>
@@ -39522,7 +39522,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>39000</v>
       </c>
@@ -39542,7 +39542,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>39500</v>
       </c>
@@ -39562,7 +39562,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>40000</v>
       </c>
@@ -39582,7 +39582,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>40500</v>
       </c>
@@ -39602,7 +39602,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>41000</v>
       </c>
@@ -39622,7 +39622,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>41500</v>
       </c>
@@ -39642,7 +39642,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>42000</v>
       </c>
@@ -39662,7 +39662,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>42500</v>
       </c>
@@ -39682,7 +39682,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>43000</v>
       </c>
@@ -39702,7 +39702,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>43500</v>
       </c>
@@ -39722,7 +39722,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>44000</v>
       </c>
@@ -39742,7 +39742,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>44500</v>
       </c>
@@ -39762,7 +39762,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>45000</v>
       </c>
@@ -39782,7 +39782,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>45500</v>
       </c>
@@ -39802,7 +39802,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>46000</v>
       </c>
@@ -39822,7 +39822,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>46500</v>
       </c>
@@ -39842,7 +39842,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>47000</v>
       </c>
@@ -39862,7 +39862,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>47500</v>
       </c>
@@ -39882,7 +39882,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>48000</v>
       </c>
@@ -39902,7 +39902,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>48500</v>
       </c>
@@ -39922,7 +39922,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>49000</v>
       </c>
@@ -39942,7 +39942,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>49500</v>
       </c>
@@ -39962,7 +39962,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>50000</v>
       </c>
@@ -39982,7 +39982,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>50500</v>
       </c>
@@ -40002,7 +40002,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>51000</v>
       </c>
@@ -40022,7 +40022,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>51500</v>
       </c>
@@ -40042,7 +40042,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>52000</v>
       </c>
@@ -40062,7 +40062,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>52500</v>
       </c>
@@ -40082,7 +40082,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>53000</v>
       </c>
@@ -40102,7 +40102,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>53500</v>
       </c>
@@ -40122,7 +40122,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>54000</v>
       </c>
@@ -40142,7 +40142,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B112">
         <v>54500</v>
       </c>
@@ -40162,7 +40162,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B113">
         <v>55000</v>
       </c>
@@ -40182,7 +40182,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B114">
         <v>55500</v>
       </c>
@@ -40202,7 +40202,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B115">
         <v>56000</v>
       </c>
@@ -40222,7 +40222,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B116">
         <v>56500</v>
       </c>
@@ -40242,7 +40242,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B117">
         <v>57000</v>
       </c>
@@ -40262,7 +40262,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B118">
         <v>57500</v>
       </c>
@@ -40282,7 +40282,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B119">
         <v>58000</v>
       </c>
@@ -40302,7 +40302,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B120">
         <v>58500</v>
       </c>
@@ -40322,7 +40322,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B121">
         <v>59000</v>
       </c>
@@ -40342,7 +40342,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B122">
         <v>59500</v>
       </c>
@@ -40362,7 +40362,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B123">
         <v>60000</v>
       </c>
@@ -40382,7 +40382,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B124">
         <v>60500</v>
       </c>
@@ -40402,7 +40402,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B125">
         <v>61000</v>
       </c>
@@ -40422,7 +40422,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B126">
         <v>61500</v>
       </c>
@@ -40442,7 +40442,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B127">
         <v>62000</v>
       </c>
@@ -40462,7 +40462,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B128">
         <v>62500</v>
       </c>
@@ -40482,7 +40482,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B129">
         <v>63000</v>
       </c>
@@ -40502,7 +40502,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>63500</v>
       </c>
@@ -40522,7 +40522,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B131">
         <v>64000</v>
       </c>
@@ -40542,7 +40542,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B132">
         <v>64500</v>
       </c>
@@ -40562,7 +40562,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B133">
         <v>65000</v>
       </c>
@@ -40582,7 +40582,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B134">
         <v>65500</v>
       </c>
@@ -40602,7 +40602,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B135">
         <v>66000</v>
       </c>
@@ -40622,7 +40622,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B136">
         <v>66500</v>
       </c>
@@ -40642,7 +40642,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B137">
         <v>67000</v>
       </c>
@@ -40662,7 +40662,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B138">
         <v>67500</v>
       </c>
@@ -40682,7 +40682,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B139">
         <v>68000</v>
       </c>
@@ -40702,7 +40702,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B140">
         <v>68500</v>
       </c>
@@ -40722,7 +40722,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B141">
         <v>69000</v>
       </c>
@@ -40742,7 +40742,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B142">
         <v>69500</v>
       </c>
@@ -40762,7 +40762,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B143">
         <v>70000</v>
       </c>
@@ -40782,7 +40782,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B144">
         <v>70500</v>
       </c>
@@ -40802,7 +40802,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B145">
         <v>71000</v>
       </c>
@@ -40822,7 +40822,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B146">
         <v>71500</v>
       </c>
@@ -40842,7 +40842,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B147">
         <v>72000</v>
       </c>
@@ -40862,7 +40862,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B148">
         <v>72500</v>
       </c>
@@ -40882,7 +40882,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B149">
         <v>73000</v>
       </c>
@@ -40902,7 +40902,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B150">
         <v>73500</v>
       </c>
@@ -40922,7 +40922,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B151">
         <v>74000</v>
       </c>
@@ -40942,7 +40942,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B152">
         <v>74500</v>
       </c>
@@ -40962,7 +40962,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B153">
         <v>75000</v>
       </c>
@@ -40982,7 +40982,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B154">
         <v>75500</v>
       </c>
@@ -41002,7 +41002,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B155">
         <v>76000</v>
       </c>
@@ -41022,7 +41022,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B156">
         <v>76500</v>
       </c>
@@ -41042,7 +41042,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B157">
         <v>77000</v>
       </c>
@@ -41062,7 +41062,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B158">
         <v>77500</v>
       </c>
@@ -41082,7 +41082,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B159">
         <v>78000</v>
       </c>
@@ -41102,7 +41102,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B160">
         <v>78500</v>
       </c>
@@ -41122,7 +41122,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B161">
         <v>79000</v>
       </c>
@@ -41142,7 +41142,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B162">
         <v>79500</v>
       </c>
@@ -41162,7 +41162,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B163">
         <v>80000</v>
       </c>
@@ -41182,7 +41182,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B164">
         <v>80500</v>
       </c>
@@ -41202,7 +41202,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B165">
         <v>81000</v>
       </c>
@@ -41222,7 +41222,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B166">
         <v>81500</v>
       </c>
@@ -41242,7 +41242,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B167">
         <v>82000</v>
       </c>
@@ -41262,7 +41262,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B168">
         <v>82500</v>
       </c>
@@ -41282,7 +41282,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B169">
         <v>83000</v>
       </c>
@@ -41302,7 +41302,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B170">
         <v>83500</v>
       </c>
@@ -41322,7 +41322,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B171">
         <v>84000</v>
       </c>
@@ -41342,7 +41342,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B172">
         <v>84500</v>
       </c>
@@ -41362,7 +41362,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B173">
         <v>85000</v>
       </c>
@@ -41382,7 +41382,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B174">
         <v>85500</v>
       </c>
@@ -41402,7 +41402,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B175">
         <v>86000</v>
       </c>
@@ -41422,7 +41422,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B176">
         <v>86500</v>
       </c>
@@ -41442,7 +41442,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B177">
         <v>87000</v>
       </c>
@@ -41462,7 +41462,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B178">
         <v>87500</v>
       </c>
@@ -41482,7 +41482,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B179">
         <v>88000</v>
       </c>
@@ -41502,7 +41502,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B180">
         <v>88500</v>
       </c>
@@ -41522,7 +41522,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B181">
         <v>89000</v>
       </c>
@@ -41542,7 +41542,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B182">
         <v>89500</v>
       </c>
@@ -41562,7 +41562,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B183">
         <v>90000</v>
       </c>
@@ -41582,7 +41582,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B184">
         <v>90500</v>
       </c>
@@ -41602,7 +41602,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B185">
         <v>91000</v>
       </c>
@@ -41622,7 +41622,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B186">
         <v>91500</v>
       </c>
@@ -41642,7 +41642,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B187">
         <v>92000</v>
       </c>
@@ -41662,7 +41662,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B188">
         <v>92500</v>
       </c>
@@ -41682,7 +41682,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B189">
         <v>93000</v>
       </c>
@@ -41702,7 +41702,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B190">
         <v>93500</v>
       </c>
@@ -41722,7 +41722,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B191">
         <v>94000</v>
       </c>
@@ -41742,7 +41742,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B192">
         <v>94500</v>
       </c>
@@ -41762,7 +41762,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B193">
         <v>95000</v>
       </c>
@@ -41782,7 +41782,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B194">
         <v>95500</v>
       </c>
@@ -41802,7 +41802,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B195">
         <v>96000</v>
       </c>
@@ -41822,7 +41822,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B196">
         <v>96500</v>
       </c>
@@ -41842,7 +41842,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B197">
         <v>97000</v>
       </c>
@@ -41862,7 +41862,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B198">
         <v>97500</v>
       </c>
@@ -41882,7 +41882,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B199">
         <v>98000</v>
       </c>
@@ -41902,7 +41902,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B200">
         <v>98500</v>
       </c>
@@ -41922,7 +41922,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B201">
         <v>99000</v>
       </c>
@@ -41942,7 +41942,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B202">
         <v>99500</v>
       </c>
